--- a/survey_templates/045_taste_test_ranking_survey--survey_templates.xlsx
+++ b/survey_templates/045_taste_test_ranking_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_title</t>
+          <t>taste_test_ranking_survey_dish_title</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Title of the dish</t>
+          <t>Dish Title</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_description</t>
+          <t>taste_test_ranking_survey_dish_description</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description of the dish</t>
+          <t>Dish Description</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_rating</t>
+          <t>taste_test_ranking_survey_rating_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rating 1</t>
+          <t>How Delicious?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_rating</t>
+          <t>taste_test_ranking_survey_rating_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rating 2</t>
+          <t>How Good?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_rating</t>
+          <t>taste_test_ranking_survey_comment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rating 3</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,19 +658,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_comment</t>
+          <t>taste_test_ranking_survey_ingredients</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Write your comment here!</t>
-        </is>
-      </c>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -680,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_ingredients</t>
+          <t>taste_test_ranking_survey_rankings</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ingredients</t>
+          <t>Rankings</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,46 +699,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_ingredients_1</t>
+          <t>taste_test_ranking_survey_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ingredient 1</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_ingredients_2</t>
+          <t>taste_test_ranking_survey_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ingredient 2</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -754,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_ingredients_3</t>
+          <t>taste_test_ranking_survey_email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ingredient 3</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -777,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_ingredients_4</t>
+          <t>taste_test_ranking_survey_phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ingredient 4</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -800,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_ingredients_5</t>
+          <t>taste_test_ranking_survey_deliciousness_rating_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ingredient 5</t>
+          <t>Taste Test Ranking Survey Deliciousness Rating 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -818,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_rankings</t>
+          <t>taste_test_ranking_survey_goodness_rating_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rankings</t>
+          <t>Taste Test Ranking Survey Goodness Rating 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -841,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_rankings</t>
+          <t>taste_test_ranking_survey_deliciousness_rating_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rankings</t>
+          <t>Taste Test Ranking Survey Deliciousness Rating 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -864,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_date</t>
+          <t>taste_test_ranking_survey_goodness_rating_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Taste Test Ranking Survey Goodness Rating 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -887,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_time</t>
+          <t>taste_test_ranking_survey_deliciousness_rating_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Taste Test Ranking Survey Deliciousness Rating 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -915,18 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_email</t>
+          <t>taste_test_ranking_survey_goodness_rating_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Taste Test Ranking Survey Goodness Rating 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -938,154 +934,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>taste_test_ranking_survey_phone</t>
+          <t>taste_test_ranking_survey_comments</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>taste_test_ranking_survey_1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Rating 1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>taste_test_ranking_survey_1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Rating 1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>taste_test_ranking_survey_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Rating 1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>taste_test_ranking_survey_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Rating 2</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>taste_test_ranking_survey_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Rating 2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>taste_test_ranking_survey_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Rating 2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1190,74 +1048,6 @@
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>Not Delicious</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>taste_test_ranking_survey_rankings_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>delicious</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Delicious</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>taste_test_ranking_survey_rankings_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>taste_test_ranking_survey_rankings_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>okay</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Okay</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>taste_test_ranking_survey_rankings_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>not_delicious</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
         <is>
           <t>Not Delicious</t>
         </is>
